--- a/artfynd/A 50065-2025 artfynd.xlsx
+++ b/artfynd/A 50065-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4766,6 +4766,321 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129728296</v>
+      </c>
+      <c r="B37" t="n">
+        <v>92907</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Gölen, Srm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>582834</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6507671</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Eva Grusell</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Eva Grusell</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129728324</v>
+      </c>
+      <c r="B38" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Gölen 3, Srm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>582832</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6507668</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Eva Grusell</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Eva Grusell</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129728316</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92907</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Gölen 1, Srm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>582839</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6507691</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Eva Grusell</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Eva Grusell</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50065-2025 artfynd.xlsx
+++ b/artfynd/A 50065-2025 artfynd.xlsx
@@ -4771,7 +4771,7 @@
         <v>129728296</v>
       </c>
       <c r="B37" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>129728324</v>
       </c>
       <c r="B38" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>129728316</v>
       </c>
       <c r="B39" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 50065-2025 artfynd.xlsx
+++ b/artfynd/A 50065-2025 artfynd.xlsx
@@ -4771,7 +4771,7 @@
         <v>129728296</v>
       </c>
       <c r="B37" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>129728324</v>
       </c>
       <c r="B38" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>129728316</v>
       </c>
       <c r="B39" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 50065-2025 artfynd.xlsx
+++ b/artfynd/A 50065-2025 artfynd.xlsx
@@ -4771,7 +4771,7 @@
         <v>129728296</v>
       </c>
       <c r="B37" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>129728324</v>
       </c>
       <c r="B38" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>129728316</v>
       </c>
       <c r="B39" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 50065-2025 artfynd.xlsx
+++ b/artfynd/A 50065-2025 artfynd.xlsx
@@ -4771,7 +4771,7 @@
         <v>129728296</v>
       </c>
       <c r="B37" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>129728324</v>
       </c>
       <c r="B38" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>129728316</v>
       </c>
       <c r="B39" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 50065-2025 artfynd.xlsx
+++ b/artfynd/A 50065-2025 artfynd.xlsx
@@ -4771,7 +4771,7 @@
         <v>129728296</v>
       </c>
       <c r="B37" t="n">
-        <v>92919</v>
+        <v>92922</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>129728324</v>
       </c>
       <c r="B38" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>129728316</v>
       </c>
       <c r="B39" t="n">
-        <v>92919</v>
+        <v>92922</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 50065-2025 artfynd.xlsx
+++ b/artfynd/A 50065-2025 artfynd.xlsx
@@ -4771,7 +4771,7 @@
         <v>129728296</v>
       </c>
       <c r="B37" t="n">
-        <v>92922</v>
+        <v>92925</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>129728324</v>
       </c>
       <c r="B38" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>129728316</v>
       </c>
       <c r="B39" t="n">
-        <v>92922</v>
+        <v>92925</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 50065-2025 artfynd.xlsx
+++ b/artfynd/A 50065-2025 artfynd.xlsx
@@ -4771,7 +4771,7 @@
         <v>129728296</v>
       </c>
       <c r="B37" t="n">
-        <v>92925</v>
+        <v>92926</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>129728324</v>
       </c>
       <c r="B38" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>129728316</v>
       </c>
       <c r="B39" t="n">
-        <v>92925</v>
+        <v>92926</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 50065-2025 artfynd.xlsx
+++ b/artfynd/A 50065-2025 artfynd.xlsx
@@ -4771,7 +4771,7 @@
         <v>129728296</v>
       </c>
       <c r="B37" t="n">
-        <v>92926</v>
+        <v>92943</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>129728324</v>
       </c>
       <c r="B38" t="n">
-        <v>92888</v>
+        <v>92905</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>129728316</v>
       </c>
       <c r="B39" t="n">
-        <v>92926</v>
+        <v>92943</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 50065-2025 artfynd.xlsx
+++ b/artfynd/A 50065-2025 artfynd.xlsx
@@ -675,62 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100737980</v>
+        <v>120319475</v>
       </c>
       <c r="B2" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>1958</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gölen, Srm</t>
+          <t>Gölen Stavsjö, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582807.1235392138</v>
+        <v>582812</v>
       </c>
       <c r="R2" t="n">
-        <v>6507739.003014503</v>
+        <v>6507689</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,7 +764,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -801,37 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103677853</v>
+        <v>103676071</v>
       </c>
       <c r="B3" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>1968</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582751.5333435655</v>
+        <v>582963</v>
       </c>
       <c r="R3" t="n">
-        <v>6507879.714018027</v>
+        <v>6507901</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -875,19 +855,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,49 +888,35 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103676382</v>
+        <v>103676096</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -968,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582802.0735576238</v>
+        <v>582927</v>
       </c>
       <c r="R4" t="n">
-        <v>6507975.904994182</v>
+        <v>6507915</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1001,19 +957,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,16 +993,11 @@
         <v>103675485</v>
       </c>
       <c r="B5" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1094,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582887.1353211638</v>
+        <v>582887</v>
       </c>
       <c r="R5" t="n">
-        <v>6507674.177764501</v>
+        <v>6507675</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1127,19 +1068,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,40 +1101,44 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103675941</v>
+        <v>111906659</v>
       </c>
       <c r="B6" t="n">
-        <v>90649</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4363</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1211,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582945.4110876017</v>
+        <v>582854</v>
       </c>
       <c r="R6" t="n">
-        <v>6507895.803443277</v>
+        <v>6507698</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1241,22 +1176,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,56 +1222,55 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103678219</v>
+        <v>111906671</v>
       </c>
       <c r="B7" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gölen Stavsjö, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582819.1389442511</v>
+        <v>582884</v>
       </c>
       <c r="R7" t="n">
-        <v>6507737.180063922</v>
+        <v>6507729</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1363,22 +1297,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,59 +1343,58 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103675260</v>
+        <v>111906689</v>
       </c>
       <c r="B8" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gölen Stavsjö, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582795.6615814221</v>
+        <v>582895</v>
       </c>
       <c r="R8" t="n">
-        <v>6507617.129761001</v>
+        <v>6507747</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1485,22 +1418,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,15 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103676567</v>
+        <v>111906800</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1547,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1572,13 +1500,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582804.7310603566</v>
+        <v>582894</v>
       </c>
       <c r="R9" t="n">
-        <v>6508022.218424885</v>
+        <v>6507781</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1602,22 +1530,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,37 +1576,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103676308</v>
+        <v>111906868</v>
       </c>
       <c r="B10" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1689,13 +1612,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582783.7469041388</v>
+        <v>582892</v>
       </c>
       <c r="R10" t="n">
-        <v>6507931.855787932</v>
+        <v>6507761</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1719,22 +1642,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1765,15 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103675240</v>
+        <v>103675941</v>
       </c>
       <c r="B11" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>4363</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1806,10 +1724,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582844.776081664</v>
+        <v>582945</v>
       </c>
       <c r="R11" t="n">
-        <v>6507682.630270858</v>
+        <v>6507896</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1839,19 +1757,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1882,15 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103676096</v>
+        <v>103675240</v>
       </c>
       <c r="B12" t="n">
-        <v>90638</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1898,21 +1801,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1968</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1923,10 +1826,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582926.7845612072</v>
+        <v>582845</v>
       </c>
       <c r="R12" t="n">
-        <v>6507914.636590956</v>
+        <v>6507683</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1956,19 +1859,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1999,56 +1892,46 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103676717</v>
+        <v>103675254</v>
       </c>
       <c r="B13" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gölen Stavsjö, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582727.9388280027</v>
+        <v>582795</v>
       </c>
       <c r="R13" t="n">
-        <v>6508082.949913389</v>
+        <v>6507617</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2078,19 +1961,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2121,37 +1994,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103676105</v>
+        <v>103676308</v>
       </c>
       <c r="B14" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2162,10 +2030,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582931.5011227399</v>
+        <v>582784</v>
       </c>
       <c r="R14" t="n">
-        <v>6507937.606271232</v>
+        <v>6507932</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2195,19 +2063,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2238,37 +2096,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103676494</v>
+        <v>111906892</v>
       </c>
       <c r="B15" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2279,13 +2132,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582818.0967691237</v>
+        <v>582868</v>
       </c>
       <c r="R15" t="n">
-        <v>6507981.444012837</v>
+        <v>6507739</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2309,22 +2162,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2355,19 +2208,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103675254</v>
+        <v>111907144</v>
       </c>
       <c r="B16" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2392,17 +2240,17 @@
       <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gölen Stavsjö, Srm</t>
+          <t>Gölen, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582795.6615814221</v>
+        <v>582758</v>
       </c>
       <c r="R16" t="n">
-        <v>6507617.129761001</v>
+        <v>6507783</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2426,22 +2274,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2472,37 +2310,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103675541</v>
+        <v>111908026</v>
       </c>
       <c r="B17" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2513,13 +2346,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582959.5371284395</v>
+        <v>582689</v>
       </c>
       <c r="R17" t="n">
-        <v>6507721.983680483</v>
+        <v>6507986</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2543,22 +2376,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2589,15 +2412,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103676071</v>
+        <v>129728324</v>
       </c>
       <c r="B18" t="n">
-        <v>90638</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2605,38 +2423,44 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1968</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gölen Stavsjö, Srm</t>
+          <t>Gölen 3, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582963.0069244684</v>
+        <v>582832</v>
       </c>
       <c r="R18" t="n">
-        <v>6507900.856994203</v>
+        <v>6507668</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2660,22 +2484,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2684,59 +2498,51 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Enoksson</t>
+          <t>Eva Grusell</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Enoksson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Lst D inventering sandbarrskogar</t>
-        </is>
-      </c>
+          <t>Eva Grusell</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103675435</v>
+        <v>103676105</v>
       </c>
       <c r="B19" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6031</v>
+        <v>4366</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2747,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582854.9202592508</v>
+        <v>582932</v>
       </c>
       <c r="R19" t="n">
-        <v>6507670.891622719</v>
+        <v>6507938</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2780,19 +2586,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2823,37 +2619,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111906892</v>
+        <v>111908119</v>
       </c>
       <c r="B20" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2864,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582867</v>
+        <v>582695</v>
       </c>
       <c r="R20" t="n">
-        <v>6507739</v>
+        <v>6508053</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2897,19 +2688,9 @@
           <t>2023-09-05</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2940,54 +2721,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111907144</v>
+        <v>111906371</v>
       </c>
       <c r="B21" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gölen, Srm</t>
+          <t>Gölen Stavsjö, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582759</v>
+        <v>582887</v>
       </c>
       <c r="R21" t="n">
-        <v>6507783</v>
+        <v>6507675</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3047,15 +2823,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111906659</v>
+        <v>111906867</v>
       </c>
       <c r="B22" t="n">
-        <v>90871</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3063,33 +2834,24 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3097,13 +2859,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582855</v>
+        <v>582892</v>
       </c>
       <c r="R22" t="n">
-        <v>6507699</v>
+        <v>6507761</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3132,7 +2894,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3142,7 +2904,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3173,15 +2935,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111906868</v>
+        <v>129728296</v>
       </c>
       <c r="B23" t="n">
-        <v>90871</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3189,35 +2946,41 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gölen Stavsjö, Srm</t>
+          <t>Gölen, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582892</v>
+        <v>582834</v>
       </c>
       <c r="R23" t="n">
-        <v>6507761</v>
+        <v>6507671</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3244,22 +3007,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3268,73 +3021,71 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Enoksson</t>
+          <t>Eva Grusell</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Enoksson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Lst D inventering sandbarrskogar</t>
-        </is>
-      </c>
+          <t>Eva Grusell</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111908119</v>
+        <v>129728316</v>
       </c>
       <c r="B24" t="n">
-        <v>90867</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gölen Stavsjö, Srm</t>
+          <t>Gölen 1, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582695</v>
+        <v>582839</v>
       </c>
       <c r="R24" t="n">
-        <v>6508053</v>
+        <v>6507691</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3361,12 +3112,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3375,59 +3126,51 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Enoksson</t>
+          <t>Eva Grusell</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Enoksson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Lst D inventering sandbarrskogar</t>
-        </is>
-      </c>
+          <t>Eva Grusell</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111906867</v>
+        <v>103675435</v>
       </c>
       <c r="B25" t="n">
-        <v>90878</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3438,13 +3181,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582892</v>
+        <v>582855</v>
       </c>
       <c r="R25" t="n">
-        <v>6507761</v>
+        <v>6507671</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3468,22 +3211,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3514,49 +3247,35 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111906689</v>
+        <v>103675541</v>
       </c>
       <c r="B26" t="n">
-        <v>90871</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2059</v>
+        <v>6031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3564,13 +3283,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582895</v>
+        <v>582959</v>
       </c>
       <c r="R26" t="n">
-        <v>6507747</v>
+        <v>6507722</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3594,22 +3313,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3640,37 +3349,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111906800</v>
+        <v>103676494</v>
       </c>
       <c r="B27" t="n">
-        <v>90871</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2059</v>
+        <v>6031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3681,13 +3385,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582894</v>
+        <v>582819</v>
       </c>
       <c r="R27" t="n">
-        <v>6507781</v>
+        <v>6507981</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3711,22 +3415,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3757,37 +3451,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111908313</v>
+        <v>111906403</v>
       </c>
       <c r="B28" t="n">
-        <v>96783</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3798,13 +3487,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582810</v>
+        <v>582927</v>
       </c>
       <c r="R28" t="n">
-        <v>6507953</v>
+        <v>6507696</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3831,19 +3520,9 @@
           <t>2023-09-05</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3874,15 +3553,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>111908234</v>
+        <v>111907792</v>
       </c>
       <c r="B29" t="n">
-        <v>5123</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3890,40 +3564,35 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>6031</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gölen Stavsjö, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582766</v>
+        <v>582669</v>
       </c>
       <c r="R29" t="n">
-        <v>6507939</v>
+        <v>6507857</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3986,63 +3655,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>111906671</v>
+        <v>111908234</v>
       </c>
       <c r="B30" t="n">
-        <v>90871</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2059</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gölen Stavsjö, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582884</v>
+        <v>582766</v>
       </c>
       <c r="R30" t="n">
-        <v>6507729</v>
+        <v>6507939</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4069,19 +3729,9 @@
           <t>2023-09-05</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>10:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4112,15 +3762,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111907792</v>
+        <v>100737980</v>
       </c>
       <c r="B31" t="n">
-        <v>90210</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4128,38 +3773,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6031</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gölen Stavsjö, Srm</t>
+          <t>Gölen, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>582669</v>
+        <v>582808</v>
       </c>
       <c r="R31" t="n">
-        <v>6507857</v>
+        <v>6507739</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4183,12 +3836,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4197,6 +3850,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4219,15 +3873,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>111908005</v>
+        <v>103675260</v>
       </c>
       <c r="B32" t="n">
-        <v>8387</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4265,13 +3914,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>582689</v>
+        <v>582795</v>
       </c>
       <c r="R32" t="n">
-        <v>6507986</v>
+        <v>6507617</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4295,12 +3944,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4331,51 +3980,51 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>111906371</v>
+        <v>103676717</v>
       </c>
       <c r="B33" t="n">
-        <v>90898</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5448</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gölen Stavsjö, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>582887</v>
+        <v>582728</v>
       </c>
       <c r="R33" t="n">
-        <v>6507674</v>
+        <v>6508083</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4402,12 +4051,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4438,15 +4087,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>111908026</v>
+        <v>103678219</v>
       </c>
       <c r="B34" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4454,38 +4098,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Gölen Stavsjö, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>582689</v>
+        <v>582819</v>
       </c>
       <c r="R34" t="n">
-        <v>6507986</v>
+        <v>6507738</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4509,12 +4158,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4545,15 +4194,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>111906403</v>
+        <v>111908005</v>
       </c>
       <c r="B35" t="n">
-        <v>90210</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4561,38 +4205,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6031</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gölen Stavsjö, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>582928</v>
+        <v>582689</v>
       </c>
       <c r="R35" t="n">
-        <v>6507696</v>
+        <v>6507986</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4652,15 +4301,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120319475</v>
+        <v>103676382</v>
       </c>
       <c r="B36" t="n">
-        <v>91591</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4668,37 +4312,47 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1958</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gölen Stavsjö, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>582812</v>
+        <v>582802</v>
       </c>
       <c r="R36" t="n">
-        <v>6507689</v>
+        <v>6507976</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4722,22 +4376,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4768,55 +4422,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129728296</v>
+        <v>103676567</v>
       </c>
       <c r="B37" t="n">
-        <v>92948</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gölen, Srm</t>
+          <t>Gölen Stavsjö, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>582834</v>
+        <v>582805</v>
       </c>
       <c r="R37" t="n">
-        <v>6507671</v>
+        <v>6508022</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4840,12 +4488,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4854,71 +4502,68 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Eva Grusell</t>
+          <t>Fredrik Enoksson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Eva Grusell</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129728324</v>
+        <v>111908313</v>
       </c>
       <c r="B38" t="n">
-        <v>92910</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gölen 3, Srm</t>
+          <t>Gölen Stavsjö, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>582832</v>
+        <v>582811</v>
       </c>
       <c r="R38" t="n">
-        <v>6507668</v>
+        <v>6507953</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4945,12 +4590,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4959,74 +4614,71 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Eva Grusell</t>
+          <t>Fredrik Enoksson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Eva Grusell</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129728316</v>
+        <v>103677853</v>
       </c>
       <c r="B39" t="n">
-        <v>92948</v>
+        <v>106244</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>221144</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gölen 1, Srm</t>
+          <t>Gölen Stavsjö, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>582839</v>
+        <v>582752</v>
       </c>
       <c r="R39" t="n">
-        <v>6507691</v>
+        <v>6507879</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5050,12 +4702,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5064,22 +4716,25 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Eva Grusell</t>
+          <t>Fredrik Enoksson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Eva Grusell</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50065-2025 artfynd.xlsx
+++ b/artfynd/A 50065-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120319475</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103676071</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103676096</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103675485</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,6 +1244,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111906659</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1340,6 +1370,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111906671</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1461,6 +1496,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111906689</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1573,6 +1613,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111906800</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1685,6 +1730,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111906868</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1787,6 +1837,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103675941</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1889,6 +1944,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103675240</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1991,6 +2051,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103675254</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2093,6 +2158,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103676308</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2205,6 +2275,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111906892</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2307,6 +2382,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111907144</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2409,6 +2489,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111908026</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2514,6 +2599,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129728324</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2616,6 +2706,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103676105</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2718,6 +2813,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111908119</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2820,6 +2920,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111906371</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2932,6 +3037,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111906867</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3037,6 +3147,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129728296</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3142,6 +3257,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129728316</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3244,6 +3364,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103675435</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3346,6 +3471,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103675541</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3448,6 +3578,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103676494</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3550,6 +3685,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111906403</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3652,6 +3792,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111907792</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3757,6 +3902,11 @@
       <c r="AY30" t="inlineStr">
         <is>
           <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111908234</t>
         </is>
       </c>
     </row>
@@ -3870,6 +4020,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100737980</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3977,6 +4132,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103675260</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4084,6 +4244,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103676717</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4191,6 +4356,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103678219</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4298,6 +4468,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111908005</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4419,6 +4594,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103676382</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4521,6 +4701,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103676567</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4633,6 +4818,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111908313</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4735,8 +4925,53 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103677853</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>